--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260313_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260313_202152.xlsx
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260313_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260313_202152.xlsx
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
